--- a/data/trans_orig/IP07C05-Estudios-trans_orig.xlsx
+++ b/data/trans_orig/IP07C05-Estudios-trans_orig.xlsx
@@ -538,7 +538,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores según frecuencia de sentirse  triste en 2007 (tasa de respuesta: 89,49%)</t>
+          <t>Menores según la frecuencia de sentirse triste en 2007 (tasa de respuesta: 89,49%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -738,7 +738,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>2316</t>
+          <t>2358</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -753,7 +753,7 @@
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>5,03%</t>
+          <t>5,12%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -808,7 +808,7 @@
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>2801</t>
+          <t>2355</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -823,7 +823,7 @@
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>3,16%</t>
+          <t>2,66%</t>
         </is>
       </c>
     </row>
@@ -851,7 +851,7 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>3917</t>
+          <t>3786</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -866,7 +866,7 @@
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>8,51%</t>
+          <t>8,23%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -886,7 +886,7 @@
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>3044</t>
+          <t>3113</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -901,7 +901,7 @@
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>7,16%</t>
+          <t>7,32%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>610</t>
+          <t>0</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>4517</t>
+          <t>5063</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -931,12 +931,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>0,69%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>5,1%</t>
+          <t>5,72%</t>
         </is>
       </c>
     </row>
@@ -959,12 +959,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>6078</t>
+          <t>6565</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>15608</t>
+          <t>15946</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -974,12 +974,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>13,21%</t>
+          <t>14,27%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>33,92%</t>
+          <t>34,65%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -994,12 +994,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>2057</t>
+          <t>1848</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>8922</t>
+          <t>8519</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1009,12 +1009,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>4,84%</t>
+          <t>4,35%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>20,99%</t>
+          <t>20,04%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1029,12 +1029,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>9579</t>
+          <t>10117</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>20974</t>
+          <t>21252</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1044,12 +1044,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>10,82%</t>
+          <t>11,43%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>23,69%</t>
+          <t>24,01%</t>
         </is>
       </c>
     </row>
@@ -1072,12 +1072,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>8664</t>
+          <t>8553</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>18899</t>
+          <t>18751</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1087,12 +1087,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>18,83%</t>
+          <t>18,59%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>41,07%</t>
+          <t>40,75%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1107,12 +1107,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>8888</t>
+          <t>9209</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>18875</t>
+          <t>19125</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1122,12 +1122,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>20,91%</t>
+          <t>21,66%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>44,41%</t>
+          <t>45,0%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1142,12 +1142,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>20902</t>
+          <t>20636</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>34584</t>
+          <t>34455</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1157,12 +1157,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>23,61%</t>
+          <t>23,31%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>39,07%</t>
+          <t>38,92%</t>
         </is>
       </c>
     </row>
@@ -1185,12 +1185,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>15122</t>
+          <t>15273</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>26042</t>
+          <t>26100</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1200,12 +1200,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>32,86%</t>
+          <t>33,19%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>56,6%</t>
+          <t>56,72%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1220,12 +1220,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>18417</t>
+          <t>18518</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>28630</t>
+          <t>28844</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1235,12 +1235,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>43,33%</t>
+          <t>43,57%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>67,36%</t>
+          <t>67,86%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1255,12 +1255,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>37362</t>
+          <t>37071</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>51785</t>
+          <t>51027</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1270,12 +1270,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>42,21%</t>
+          <t>41,88%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>58,5%</t>
+          <t>57,65%</t>
         </is>
       </c>
     </row>
@@ -1420,7 +1420,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>4698</t>
+          <t>4308</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1435,7 +1435,7 @@
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>2,48%</t>
+          <t>2,27%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1455,7 +1455,7 @@
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>3008</t>
+          <t>3403</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1470,7 +1470,7 @@
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>1,39%</t>
+          <t>1,57%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1485,12 +1485,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>596</t>
+          <t>593</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>5123</t>
+          <t>5837</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1505,7 +1505,7 @@
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>1,26%</t>
+          <t>1,44%</t>
         </is>
       </c>
     </row>
@@ -1528,12 +1528,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>1231</t>
+          <t>1248</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>7793</t>
+          <t>7006</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1543,12 +1543,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>0,65%</t>
+          <t>0,66%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>4,11%</t>
+          <t>3,69%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1568,7 +1568,7 @@
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>2940</t>
+          <t>2484</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1583,7 +1583,7 @@
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>1,36%</t>
+          <t>1,15%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1598,12 +1598,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>1450</t>
+          <t>1224</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>7911</t>
+          <t>8197</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1613,12 +1613,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>0,36%</t>
+          <t>0,3%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>1,95%</t>
+          <t>2,02%</t>
         </is>
       </c>
     </row>
@@ -1641,12 +1641,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>14807</t>
+          <t>14496</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>29206</t>
+          <t>27860</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1656,12 +1656,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>7,81%</t>
+          <t>7,64%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>15,4%</t>
+          <t>14,69%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1676,12 +1676,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>15937</t>
+          <t>16540</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>31093</t>
+          <t>30517</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1691,12 +1691,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>7,35%</t>
+          <t>7,63%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>14,34%</t>
+          <t>14,07%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1711,12 +1711,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>34267</t>
+          <t>35229</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>55437</t>
+          <t>55202</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1726,12 +1726,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>8,43%</t>
+          <t>8,67%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>13,64%</t>
+          <t>13,58%</t>
         </is>
       </c>
     </row>
@@ -1754,12 +1754,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>39152</t>
+          <t>39491</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>58686</t>
+          <t>57462</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1769,12 +1769,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>20,64%</t>
+          <t>20,82%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>30,94%</t>
+          <t>30,3%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1789,12 +1789,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>37940</t>
+          <t>37918</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>57433</t>
+          <t>56682</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1804,12 +1804,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>17,5%</t>
+          <t>17,49%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>26,49%</t>
+          <t>26,14%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1824,12 +1824,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>81612</t>
+          <t>81297</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>108799</t>
+          <t>110596</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1839,12 +1839,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>20,08%</t>
+          <t>20,0%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>26,77%</t>
+          <t>27,21%</t>
         </is>
       </c>
     </row>
@@ -1867,12 +1867,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>105671</t>
+          <t>105331</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>126904</t>
+          <t>125785</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1882,12 +1882,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>55,72%</t>
+          <t>55,54%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>66,91%</t>
+          <t>66,32%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1902,12 +1902,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>134559</t>
+          <t>135794</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>157378</t>
+          <t>156052</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1917,12 +1917,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>62,06%</t>
+          <t>62,63%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>72,58%</t>
+          <t>71,97%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1937,12 +1937,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>247817</t>
+          <t>245780</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>276938</t>
+          <t>276448</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1952,12 +1952,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>60,97%</t>
+          <t>60,46%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>68,13%</t>
+          <t>68,01%</t>
         </is>
       </c>
     </row>
@@ -2102,7 +2102,7 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>2742</t>
+          <t>2996</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2117,7 +2117,7 @@
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>5,12%</t>
+          <t>5,6%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2137,7 +2137,7 @@
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>4455</t>
+          <t>4504</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2152,7 +2152,7 @@
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>9,08%</t>
+          <t>9,18%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2167,12 +2167,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>525</t>
+          <t>537</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>5015</t>
+          <t>5519</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2182,12 +2182,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>0,51%</t>
+          <t>0,52%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>4,89%</t>
+          <t>5,38%</t>
         </is>
       </c>
     </row>
@@ -2215,7 +2215,7 @@
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>3938</t>
+          <t>4208</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2230,7 +2230,7 @@
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>7,36%</t>
+          <t>7,86%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2250,7 +2250,7 @@
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>3527</t>
+          <t>3211</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2265,7 +2265,7 @@
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>7,19%</t>
+          <t>6,55%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2285,7 +2285,7 @@
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>4586</t>
+          <t>5000</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2300,7 +2300,7 @@
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>4,47%</t>
+          <t>4,87%</t>
         </is>
       </c>
     </row>
@@ -2323,12 +2323,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>4177</t>
+          <t>3871</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>12761</t>
+          <t>12970</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -2338,12 +2338,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>7,8%</t>
+          <t>7,23%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>23,84%</t>
+          <t>24,23%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -2358,12 +2358,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>1343</t>
+          <t>1321</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>7414</t>
+          <t>7507</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2373,12 +2373,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>2,74%</t>
+          <t>2,69%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>15,12%</t>
+          <t>15,31%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -2393,12 +2393,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>6391</t>
+          <t>6596</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>16744</t>
+          <t>17138</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -2408,12 +2408,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>6,23%</t>
+          <t>6,43%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>16,32%</t>
+          <t>16,71%</t>
         </is>
       </c>
     </row>
@@ -2436,12 +2436,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>8965</t>
+          <t>9447</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>19571</t>
+          <t>19735</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2451,12 +2451,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>16,75%</t>
+          <t>17,65%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>36,56%</t>
+          <t>36,87%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2471,12 +2471,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>8327</t>
+          <t>8109</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>18599</t>
+          <t>18033</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2486,12 +2486,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>16,98%</t>
+          <t>16,54%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>37,93%</t>
+          <t>36,77%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2506,12 +2506,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>19709</t>
+          <t>19500</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>33765</t>
+          <t>34500</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2521,12 +2521,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>19,22%</t>
+          <t>19,01%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>32,92%</t>
+          <t>33,64%</t>
         </is>
       </c>
     </row>
@@ -2549,12 +2549,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>24680</t>
+          <t>24678</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>36315</t>
+          <t>36822</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2564,12 +2564,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>46,11%</t>
+          <t>46,1%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>67,85%</t>
+          <t>68,79%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2584,12 +2584,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>25390</t>
+          <t>25447</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>36095</t>
+          <t>36722</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2599,12 +2599,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>51,77%</t>
+          <t>51,89%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>73,6%</t>
+          <t>74,88%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2619,12 +2619,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>54215</t>
+          <t>53738</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>69827</t>
+          <t>69790</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2634,12 +2634,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>52,86%</t>
+          <t>52,39%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>68,08%</t>
+          <t>68,04%</t>
         </is>
       </c>
     </row>
@@ -2779,12 +2779,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>683</t>
+          <t>655</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>5629</t>
+          <t>5757</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2794,12 +2794,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>0,24%</t>
+          <t>0,23%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>1,95%</t>
+          <t>1,99%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2814,12 +2814,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>593</t>
+          <t>592</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>5180</t>
+          <t>5557</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2834,7 +2834,7 @@
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>1,68%</t>
+          <t>1,8%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2849,12 +2849,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>1748</t>
+          <t>1798</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>8530</t>
+          <t>8359</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2864,12 +2864,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>0,29%</t>
+          <t>0,3%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>1,43%</t>
+          <t>1,4%</t>
         </is>
       </c>
     </row>
@@ -2892,12 +2892,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>2127</t>
+          <t>2590</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>9892</t>
+          <t>9736</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2907,12 +2907,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>0,74%</t>
+          <t>0,9%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>3,42%</t>
+          <t>3,37%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2927,12 +2927,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>485</t>
+          <t>488</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>5244</t>
+          <t>5399</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2947,7 +2947,7 @@
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>1,7%</t>
+          <t>1,75%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2962,12 +2962,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>3271</t>
+          <t>3582</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>11547</t>
+          <t>12565</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -2977,12 +2977,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>0,55%</t>
+          <t>0,6%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>1,93%</t>
+          <t>2,1%</t>
         </is>
       </c>
     </row>
@@ -3005,12 +3005,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>30262</t>
+          <t>30828</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>49014</t>
+          <t>49216</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -3020,12 +3020,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>10,46%</t>
+          <t>10,66%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>16,95%</t>
+          <t>17,02%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -3040,12 +3040,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>23304</t>
+          <t>23296</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>39896</t>
+          <t>40169</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -3055,12 +3055,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>7,56%</t>
+          <t>7,55%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>12,94%</t>
+          <t>13,03%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -3075,12 +3075,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>58101</t>
+          <t>56219</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>82982</t>
+          <t>82463</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -3090,12 +3090,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>9,72%</t>
+          <t>9,41%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>13,89%</t>
+          <t>13,8%</t>
         </is>
       </c>
     </row>
@@ -3118,12 +3118,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>63627</t>
+          <t>64658</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>88073</t>
+          <t>88139</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3133,12 +3133,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>22,0%</t>
+          <t>22,36%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>30,45%</t>
+          <t>30,48%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3153,12 +3153,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>62703</t>
+          <t>63137</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>87159</t>
+          <t>87848</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3168,12 +3168,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>20,33%</t>
+          <t>20,47%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>28,26%</t>
+          <t>28,49%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3188,12 +3188,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>132883</t>
+          <t>133695</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>168515</t>
+          <t>168752</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3203,12 +3203,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>22,24%</t>
+          <t>22,37%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>28,2%</t>
+          <t>28,24%</t>
         </is>
       </c>
     </row>
@@ -3231,12 +3231,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>154087</t>
+          <t>154549</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>180241</t>
+          <t>180259</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3246,7 +3246,7 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>53,28%</t>
+          <t>53,44%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
@@ -3266,12 +3266,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>186682</t>
+          <t>186257</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>213346</t>
+          <t>212644</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -3281,12 +3281,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>60,54%</t>
+          <t>60,4%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>69,18%</t>
+          <t>68,96%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3301,12 +3301,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>348536</t>
+          <t>348355</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>385780</t>
+          <t>385785</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3316,7 +3316,7 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>58,33%</t>
+          <t>58,3%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
@@ -3497,7 +3497,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores según frecuencia de sentirse  triste en 2012 (tasa de respuesta: 95,72%)</t>
+          <t>Menores según la frecuencia de sentirse triste en 2012 (tasa de respuesta: 95,72%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -3697,7 +3697,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>3145</t>
+          <t>3189</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -3712,7 +3712,7 @@
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>6,09%</t>
+          <t>6,18%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -3732,7 +3732,7 @@
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>4123</t>
+          <t>4313</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -3747,7 +3747,7 @@
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>9,13%</t>
+          <t>9,55%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -3767,7 +3767,7 @@
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>4753</t>
+          <t>4791</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -3782,7 +3782,7 @@
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>4,91%</t>
+          <t>4,95%</t>
         </is>
       </c>
     </row>
@@ -3810,7 +3810,7 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>3191</t>
+          <t>4112</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -3825,7 +3825,7 @@
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>6,18%</t>
+          <t>7,97%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -3880,7 +3880,7 @@
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>3611</t>
+          <t>3144</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -3895,7 +3895,7 @@
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>3,73%</t>
+          <t>3,25%</t>
         </is>
       </c>
     </row>
@@ -3918,12 +3918,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>7117</t>
+          <t>7129</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>17203</t>
+          <t>17503</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -3933,12 +3933,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>13,79%</t>
+          <t>13,81%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>33,32%</t>
+          <t>33,9%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -3953,12 +3953,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>6114</t>
+          <t>6029</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>16151</t>
+          <t>15733</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -3968,12 +3968,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>13,54%</t>
+          <t>13,35%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>35,76%</t>
+          <t>34,84%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -3988,12 +3988,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>15492</t>
+          <t>15203</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>29548</t>
+          <t>29127</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -4003,12 +4003,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>16,01%</t>
+          <t>15,71%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>30,53%</t>
+          <t>30,09%</t>
         </is>
       </c>
     </row>
@@ -4031,12 +4031,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>11916</t>
+          <t>12358</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>23616</t>
+          <t>24023</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -4046,12 +4046,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>23,08%</t>
+          <t>23,94%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>45,74%</t>
+          <t>46,53%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -4066,12 +4066,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>10920</t>
+          <t>10935</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>22051</t>
+          <t>21433</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -4081,12 +4081,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>24,18%</t>
+          <t>24,21%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>48,83%</t>
+          <t>47,46%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -4101,12 +4101,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>26082</t>
+          <t>25809</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>41240</t>
+          <t>42200</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -4116,12 +4116,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>26,95%</t>
+          <t>26,67%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>42,61%</t>
+          <t>43,6%</t>
         </is>
       </c>
     </row>
@@ -4144,12 +4144,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>14973</t>
+          <t>15240</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>26832</t>
+          <t>27329</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -4159,12 +4159,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>29,0%</t>
+          <t>29,52%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>51,97%</t>
+          <t>52,94%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -4179,12 +4179,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>12834</t>
+          <t>12589</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>24167</t>
+          <t>23518</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -4194,12 +4194,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>28,42%</t>
+          <t>27,87%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>53,51%</t>
+          <t>52,08%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -4214,12 +4214,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>31589</t>
+          <t>31008</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>46743</t>
+          <t>47064</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -4229,12 +4229,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>32,64%</t>
+          <t>32,04%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>48,29%</t>
+          <t>48,63%</t>
         </is>
       </c>
     </row>
@@ -4374,12 +4374,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>772</t>
+          <t>775</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>7091</t>
+          <t>7408</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -4394,7 +4394,7 @@
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>3,55%</t>
+          <t>3,71%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -4409,12 +4409,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>575</t>
+          <t>577</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>5456</t>
+          <t>5212</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -4429,7 +4429,7 @@
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>2,43%</t>
+          <t>2,32%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -4444,12 +4444,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>2355</t>
+          <t>2142</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>10408</t>
+          <t>10101</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -4459,12 +4459,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>0,55%</t>
+          <t>0,5%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>2,45%</t>
+          <t>2,38%</t>
         </is>
       </c>
     </row>
@@ -4487,12 +4487,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>2808</t>
+          <t>2624</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>11408</t>
+          <t>10372</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -4502,12 +4502,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>1,41%</t>
+          <t>1,31%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>5,71%</t>
+          <t>5,19%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -4522,12 +4522,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>1393</t>
+          <t>1509</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>8216</t>
+          <t>7869</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -4537,12 +4537,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>0,62%</t>
+          <t>0,67%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>3,66%</t>
+          <t>3,5%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -4557,12 +4557,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>5715</t>
+          <t>5444</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>15951</t>
+          <t>15751</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -4572,12 +4572,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>1,35%</t>
+          <t>1,28%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>3,76%</t>
+          <t>3,71%</t>
         </is>
       </c>
     </row>
@@ -4600,12 +4600,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>28893</t>
+          <t>28942</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>47563</t>
+          <t>47294</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -4615,12 +4615,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>14,46%</t>
+          <t>14,49%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>23,81%</t>
+          <t>23,68%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -4635,12 +4635,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>34876</t>
+          <t>34062</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>54647</t>
+          <t>53950</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -4650,12 +4650,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>15,52%</t>
+          <t>15,15%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>24,31%</t>
+          <t>24,0%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -4670,12 +4670,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>69072</t>
+          <t>68094</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>94995</t>
+          <t>96114</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -4685,12 +4685,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>16,27%</t>
+          <t>16,04%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>22,38%</t>
+          <t>22,64%</t>
         </is>
       </c>
     </row>
@@ -4713,12 +4713,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>51146</t>
+          <t>51359</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>71616</t>
+          <t>72536</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -4728,12 +4728,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>25,61%</t>
+          <t>25,71%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>35,85%</t>
+          <t>36,31%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -4748,12 +4748,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>55117</t>
+          <t>54722</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>77782</t>
+          <t>76971</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -4763,12 +4763,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>24,52%</t>
+          <t>24,35%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>34,61%</t>
+          <t>34,25%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -4783,12 +4783,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>111438</t>
+          <t>111391</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>142765</t>
+          <t>142734</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -4798,12 +4798,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>26,25%</t>
+          <t>26,24%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>33,63%</t>
+          <t>33,62%</t>
         </is>
       </c>
     </row>
@@ -4826,12 +4826,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>81688</t>
+          <t>81319</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>104301</t>
+          <t>104001</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -4841,12 +4841,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>40,9%</t>
+          <t>40,71%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>52,22%</t>
+          <t>52,07%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -4861,12 +4861,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>98023</t>
+          <t>98118</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>122550</t>
+          <t>122458</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -4876,12 +4876,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>43,61%</t>
+          <t>43,65%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>54,52%</t>
+          <t>54,48%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -4896,12 +4896,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>184608</t>
+          <t>185753</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>218305</t>
+          <t>219921</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -4911,12 +4911,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>43,49%</t>
+          <t>43,76%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>51,42%</t>
+          <t>51,81%</t>
         </is>
       </c>
     </row>
@@ -5056,12 +5056,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>1361</t>
+          <t>1362</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>7711</t>
+          <t>8413</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -5076,7 +5076,7 @@
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>12,68%</t>
+          <t>13,84%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -5096,7 +5096,7 @@
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>3072</t>
+          <t>3678</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -5111,7 +5111,7 @@
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>5,47%</t>
+          <t>6,55%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -5126,12 +5126,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>1563</t>
+          <t>1841</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>8827</t>
+          <t>8575</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -5141,12 +5141,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>1,34%</t>
+          <t>1,57%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>7,55%</t>
+          <t>7,33%</t>
         </is>
       </c>
     </row>
@@ -5174,7 +5174,7 @@
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>3795</t>
+          <t>3854</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -5189,7 +5189,7 @@
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>6,24%</t>
+          <t>6,34%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -5209,7 +5209,7 @@
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>3761</t>
+          <t>3914</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -5224,7 +5224,7 @@
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>6,7%</t>
+          <t>6,97%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -5244,7 +5244,7 @@
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>4947</t>
+          <t>5320</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -5259,7 +5259,7 @@
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>4,23%</t>
+          <t>4,55%</t>
         </is>
       </c>
     </row>
@@ -5282,12 +5282,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>7933</t>
+          <t>7924</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>18122</t>
+          <t>17952</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -5297,12 +5297,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>13,05%</t>
+          <t>13,03%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>29,81%</t>
+          <t>29,53%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -5317,12 +5317,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>6558</t>
+          <t>6708</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>16130</t>
+          <t>16084</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -5332,12 +5332,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>11,68%</t>
+          <t>11,95%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>28,73%</t>
+          <t>28,64%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -5352,12 +5352,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>15976</t>
+          <t>16778</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>30680</t>
+          <t>31026</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -5367,12 +5367,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>13,66%</t>
+          <t>14,35%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>26,23%</t>
+          <t>26,53%</t>
         </is>
       </c>
     </row>
@@ -5395,12 +5395,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>13241</t>
+          <t>12874</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>25219</t>
+          <t>25676</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -5410,12 +5410,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>21,78%</t>
+          <t>21,17%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>41,48%</t>
+          <t>42,23%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -5430,12 +5430,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>14178</t>
+          <t>14246</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>25326</t>
+          <t>25571</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -5445,12 +5445,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>25,25%</t>
+          <t>25,37%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>45,1%</t>
+          <t>45,54%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -5465,12 +5465,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>30113</t>
+          <t>30403</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>46680</t>
+          <t>47422</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -5480,12 +5480,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>25,75%</t>
+          <t>26,0%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>39,91%</t>
+          <t>40,55%</t>
         </is>
       </c>
     </row>
@@ -5508,12 +5508,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>19294</t>
+          <t>19262</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>31766</t>
+          <t>32236</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -5523,12 +5523,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>31,73%</t>
+          <t>31,68%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>52,25%</t>
+          <t>53,02%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -5543,12 +5543,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>18805</t>
+          <t>18859</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>30752</t>
+          <t>31177</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -5558,12 +5558,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>33,49%</t>
+          <t>33,59%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>54,77%</t>
+          <t>55,52%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -5578,12 +5578,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>41029</t>
+          <t>41543</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>58584</t>
+          <t>58569</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -5593,12 +5593,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>35,08%</t>
+          <t>35,52%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>50,09%</t>
+          <t>50,08%</t>
         </is>
       </c>
     </row>
@@ -5738,12 +5738,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>3896</t>
+          <t>3823</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>13110</t>
+          <t>12860</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -5753,12 +5753,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>1,25%</t>
+          <t>1,22%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>4,2%</t>
+          <t>4,12%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -5773,12 +5773,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>1231</t>
+          <t>1264</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>7606</t>
+          <t>7294</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -5788,12 +5788,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>0,38%</t>
+          <t>0,39%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>2,33%</t>
+          <t>2,24%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -5808,12 +5808,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>6065</t>
+          <t>6203</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>16884</t>
+          <t>16646</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -5823,12 +5823,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>0,95%</t>
+          <t>0,97%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>2,65%</t>
+          <t>2,61%</t>
         </is>
       </c>
     </row>
@@ -5851,12 +5851,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>3869</t>
+          <t>3908</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>12417</t>
+          <t>13045</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -5866,12 +5866,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>1,24%</t>
+          <t>1,25%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>3,98%</t>
+          <t>4,18%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -5886,12 +5886,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>2009</t>
+          <t>1838</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>9615</t>
+          <t>9116</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -5901,12 +5901,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>0,62%</t>
+          <t>0,56%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>2,95%</t>
+          <t>2,8%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -5921,12 +5921,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>7373</t>
+          <t>7302</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>17877</t>
+          <t>18753</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -5936,12 +5936,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>1,16%</t>
+          <t>1,14%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>2,8%</t>
+          <t>2,94%</t>
         </is>
       </c>
     </row>
@@ -5964,12 +5964,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>50587</t>
+          <t>49945</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>74691</t>
+          <t>73421</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -5979,12 +5979,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>16,2%</t>
+          <t>16,0%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>23,93%</t>
+          <t>23,52%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -5999,12 +5999,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>53156</t>
+          <t>53936</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>76048</t>
+          <t>78356</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -6014,12 +6014,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>16,3%</t>
+          <t>16,54%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>23,32%</t>
+          <t>24,03%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -6034,12 +6034,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>110361</t>
+          <t>109637</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>143981</t>
+          <t>146016</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -6049,12 +6049,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>17,29%</t>
+          <t>17,18%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>22,56%</t>
+          <t>22,88%</t>
         </is>
       </c>
     </row>
@@ -6077,12 +6077,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>84006</t>
+          <t>85220</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>111273</t>
+          <t>112037</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -6092,12 +6092,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>26,91%</t>
+          <t>27,3%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>35,64%</t>
+          <t>35,89%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -6112,12 +6112,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>86767</t>
+          <t>88411</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>114854</t>
+          <t>115306</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -6127,12 +6127,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>26,61%</t>
+          <t>27,11%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>35,22%</t>
+          <t>35,36%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -6147,12 +6147,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>180477</t>
+          <t>177593</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>219074</t>
+          <t>219497</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -6162,12 +6162,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>28,28%</t>
+          <t>27,82%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>34,32%</t>
+          <t>34,39%</t>
         </is>
       </c>
     </row>
@@ -6190,12 +6190,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>124094</t>
+          <t>124169</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>153226</t>
+          <t>151750</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -6205,12 +6205,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>39,75%</t>
+          <t>39,78%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>49,08%</t>
+          <t>48,61%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -6225,12 +6225,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>137260</t>
+          <t>137110</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>166767</t>
+          <t>165951</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -6240,12 +6240,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>42,09%</t>
+          <t>42,05%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>51,14%</t>
+          <t>50,89%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -6260,12 +6260,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>270628</t>
+          <t>269591</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>311839</t>
+          <t>311060</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -6275,12 +6275,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>42,4%</t>
+          <t>42,24%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>48,86%</t>
+          <t>48,74%</t>
         </is>
       </c>
     </row>
@@ -6456,7 +6456,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores según frecuencia de sentirse  triste en 2016 (tasa de respuesta: 95,77%)</t>
+          <t>Menores según la frecuencia de sentirse triste en 2016 (tasa de respuesta: 95,77%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -6691,7 +6691,7 @@
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>4937</t>
+          <t>4867</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -6706,7 +6706,7 @@
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>13,47%</t>
+          <t>13,28%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -6726,7 +6726,7 @@
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>4701</t>
+          <t>4612</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -6741,7 +6741,7 @@
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>6,99%</t>
+          <t>6,86%</t>
         </is>
       </c>
     </row>
@@ -6769,7 +6769,7 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>4241</t>
+          <t>3861</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -6784,7 +6784,7 @@
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>13,86%</t>
+          <t>12,61%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -6804,7 +6804,7 @@
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>3944</t>
+          <t>3969</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -6819,7 +6819,7 @@
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>10,76%</t>
+          <t>10,83%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -6839,7 +6839,7 @@
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>5498</t>
+          <t>5176</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -6849,12 +6849,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>0,9%</t>
+          <t>0,91%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>8,18%</t>
+          <t>7,7%</t>
         </is>
       </c>
     </row>
@@ -6877,12 +6877,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>3026</t>
+          <t>3218</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>10182</t>
+          <t>10833</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -6892,12 +6892,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>9,89%</t>
+          <t>10,51%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>33,27%</t>
+          <t>35,39%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -6912,12 +6912,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>656</t>
+          <t>643</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>6001</t>
+          <t>6334</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -6927,12 +6927,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>1,79%</t>
+          <t>1,76%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>16,38%</t>
+          <t>17,29%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -6947,12 +6947,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>4918</t>
+          <t>4851</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>13941</t>
+          <t>14648</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -6962,12 +6962,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>7,31%</t>
+          <t>7,21%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>20,73%</t>
+          <t>21,78%</t>
         </is>
       </c>
     </row>
@@ -6990,12 +6990,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>4898</t>
+          <t>5105</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>13244</t>
+          <t>13719</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -7005,12 +7005,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>16,0%</t>
+          <t>16,68%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>43,27%</t>
+          <t>44,83%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -7025,12 +7025,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>7021</t>
+          <t>7120</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>16117</t>
+          <t>16657</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -7040,12 +7040,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>19,16%</t>
+          <t>19,43%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>43,99%</t>
+          <t>45,46%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -7060,12 +7060,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>14452</t>
+          <t>13792</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>26687</t>
+          <t>26206</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -7075,12 +7075,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>21,49%</t>
+          <t>20,51%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>39,69%</t>
+          <t>38,97%</t>
         </is>
       </c>
     </row>
@@ -7103,12 +7103,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>10080</t>
+          <t>9658</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>19334</t>
+          <t>18829</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -7118,12 +7118,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>32,94%</t>
+          <t>31,55%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>63,17%</t>
+          <t>61,52%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -7138,12 +7138,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>16239</t>
+          <t>15906</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>26126</t>
+          <t>25903</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -7153,12 +7153,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>44,32%</t>
+          <t>43,41%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>71,31%</t>
+          <t>70,7%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -7173,12 +7173,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>28557</t>
+          <t>28958</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>42056</t>
+          <t>42444</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -7188,12 +7188,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>42,47%</t>
+          <t>43,06%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>62,54%</t>
+          <t>63,12%</t>
         </is>
       </c>
     </row>
@@ -7333,12 +7333,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>527</t>
+          <t>522</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>4946</t>
+          <t>4739</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -7348,12 +7348,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>0,22%</t>
+          <t>0,21%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>2,03%</t>
+          <t>1,94%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -7373,7 +7373,7 @@
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>3491</t>
+          <t>3211</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -7388,7 +7388,7 @@
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>1,47%</t>
+          <t>1,35%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -7403,12 +7403,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>643</t>
+          <t>641</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>5785</t>
+          <t>5770</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -7446,12 +7446,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>2757</t>
+          <t>2854</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>12161</t>
+          <t>11745</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -7461,12 +7461,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>1,13%</t>
+          <t>1,17%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>4,98%</t>
+          <t>4,81%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -7481,12 +7481,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>568</t>
+          <t>565</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>5147</t>
+          <t>4996</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -7501,7 +7501,7 @@
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>2,17%</t>
+          <t>2,11%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -7516,12 +7516,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>4471</t>
+          <t>4305</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>13719</t>
+          <t>13711</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -7531,7 +7531,7 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>0,93%</t>
+          <t>0,89%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
@@ -7559,12 +7559,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>30501</t>
+          <t>30655</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>49964</t>
+          <t>49724</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -7574,12 +7574,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>12,5%</t>
+          <t>12,56%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>20,48%</t>
+          <t>20,38%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -7594,12 +7594,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>24625</t>
+          <t>24005</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>42484</t>
+          <t>42482</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -7609,7 +7609,7 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>10,39%</t>
+          <t>10,13%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
@@ -7629,12 +7629,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>60735</t>
+          <t>59914</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>87331</t>
+          <t>85721</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -7644,12 +7644,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>12,63%</t>
+          <t>12,45%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>18,15%</t>
+          <t>17,82%</t>
         </is>
       </c>
     </row>
@@ -7672,12 +7672,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>64050</t>
+          <t>64515</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>89497</t>
+          <t>88774</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -7687,12 +7687,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>26,25%</t>
+          <t>26,44%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>36,68%</t>
+          <t>36,38%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -7707,12 +7707,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>71456</t>
+          <t>71426</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>95749</t>
+          <t>95553</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -7722,12 +7722,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>30,14%</t>
+          <t>30,13%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>40,39%</t>
+          <t>40,31%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -7742,12 +7742,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>140983</t>
+          <t>144108</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>175679</t>
+          <t>176554</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -7757,12 +7757,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>29,31%</t>
+          <t>29,96%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>36,52%</t>
+          <t>36,7%</t>
         </is>
       </c>
     </row>
@@ -7785,12 +7785,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>108328</t>
+          <t>108210</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>134811</t>
+          <t>133673</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -7800,12 +7800,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>44,4%</t>
+          <t>44,35%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>55,25%</t>
+          <t>54,78%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -7820,12 +7820,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>106080</t>
+          <t>106401</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>132054</t>
+          <t>131326</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -7835,12 +7835,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>44,75%</t>
+          <t>44,88%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>55,7%</t>
+          <t>55,4%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -7855,12 +7855,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>222646</t>
+          <t>219671</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>258479</t>
+          <t>255966</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -7870,12 +7870,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>46,28%</t>
+          <t>45,66%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>53,73%</t>
+          <t>53,21%</t>
         </is>
       </c>
     </row>
@@ -8133,7 +8133,7 @@
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>4039</t>
+          <t>3925</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -8148,7 +8148,7 @@
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>5,68%</t>
+          <t>5,52%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -8168,7 +8168,7 @@
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>3637</t>
+          <t>4111</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -8183,7 +8183,7 @@
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>4,82%</t>
+          <t>5,45%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -8203,7 +8203,7 @@
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>5243</t>
+          <t>5439</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -8218,7 +8218,7 @@
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>3,58%</t>
+          <t>3,71%</t>
         </is>
       </c>
     </row>
@@ -8241,12 +8241,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>7681</t>
+          <t>6971</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>18806</t>
+          <t>17777</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -8256,12 +8256,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>10,8%</t>
+          <t>9,81%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>26,45%</t>
+          <t>25,01%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -8276,12 +8276,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>5528</t>
+          <t>5971</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>15471</t>
+          <t>15097</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -8291,12 +8291,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>7,32%</t>
+          <t>7,91%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>20,49%</t>
+          <t>20,0%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -8311,12 +8311,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>14900</t>
+          <t>15517</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>29404</t>
+          <t>29867</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -8326,12 +8326,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>10,16%</t>
+          <t>10,59%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>20,06%</t>
+          <t>20,37%</t>
         </is>
       </c>
     </row>
@@ -8354,12 +8354,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>21835</t>
+          <t>22095</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>35713</t>
+          <t>36394</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -8369,12 +8369,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>30,71%</t>
+          <t>31,08%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>50,24%</t>
+          <t>51,19%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -8389,12 +8389,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>19287</t>
+          <t>19225</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>32933</t>
+          <t>33017</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -8404,47 +8404,47 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>25,54%</t>
+          <t>25,46%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
+          <t>43,73%</t>
+        </is>
+      </c>
+      <c r="Q19" s="2" t="inlineStr">
+        <is>
+          <t>77</t>
+        </is>
+      </c>
+      <c r="R19" s="2" t="inlineStr">
+        <is>
+          <t>54590</t>
+        </is>
+      </c>
+      <c r="S19" s="2" t="inlineStr">
+        <is>
+          <t>44958</t>
+        </is>
+      </c>
+      <c r="T19" s="2" t="inlineStr">
+        <is>
+          <t>63943</t>
+        </is>
+      </c>
+      <c r="U19" s="2" t="inlineStr">
+        <is>
+          <t>37,24%</t>
+        </is>
+      </c>
+      <c r="V19" s="2" t="inlineStr">
+        <is>
+          <t>30,67%</t>
+        </is>
+      </c>
+      <c r="W19" s="2" t="inlineStr">
+        <is>
           <t>43,62%</t>
-        </is>
-      </c>
-      <c r="Q19" s="2" t="inlineStr">
-        <is>
-          <t>77</t>
-        </is>
-      </c>
-      <c r="R19" s="2" t="inlineStr">
-        <is>
-          <t>54590</t>
-        </is>
-      </c>
-      <c r="S19" s="2" t="inlineStr">
-        <is>
-          <t>45293</t>
-        </is>
-      </c>
-      <c r="T19" s="2" t="inlineStr">
-        <is>
-          <t>64411</t>
-        </is>
-      </c>
-      <c r="U19" s="2" t="inlineStr">
-        <is>
-          <t>37,24%</t>
-        </is>
-      </c>
-      <c r="V19" s="2" t="inlineStr">
-        <is>
-          <t>30,9%</t>
-        </is>
-      </c>
-      <c r="W19" s="2" t="inlineStr">
-        <is>
-          <t>43,94%</t>
         </is>
       </c>
     </row>
@@ -8467,12 +8467,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>21719</t>
+          <t>23002</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>35634</t>
+          <t>36169</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -8482,12 +8482,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>30,55%</t>
+          <t>32,36%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>50,13%</t>
+          <t>50,88%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -8502,12 +8502,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>31896</t>
+          <t>32632</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>46295</t>
+          <t>46984</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -8517,12 +8517,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>42,25%</t>
+          <t>43,22%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>61,32%</t>
+          <t>62,23%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -8537,12 +8537,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>58825</t>
+          <t>58868</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>78903</t>
+          <t>79191</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -8552,12 +8552,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>40,13%</t>
+          <t>40,16%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>53,82%</t>
+          <t>54,02%</t>
         </is>
       </c>
     </row>
@@ -8697,12 +8697,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>522</t>
+          <t>520</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>4523</t>
+          <t>4450</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -8717,7 +8717,7 @@
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>1,31%</t>
+          <t>1,29%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -8737,7 +8737,7 @@
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>5268</t>
+          <t>6194</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -8752,7 +8752,7 @@
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>1,51%</t>
+          <t>1,77%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -8767,12 +8767,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>1141</t>
+          <t>1162</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>7427</t>
+          <t>7460</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -8782,7 +8782,7 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>0,16%</t>
+          <t>0,17%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
@@ -8810,12 +8810,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>4564</t>
+          <t>4587</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>14243</t>
+          <t>13768</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -8825,12 +8825,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>1,32%</t>
+          <t>1,33%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>4,12%</t>
+          <t>3,98%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -8845,12 +8845,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>1235</t>
+          <t>1226</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>6884</t>
+          <t>7250</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -8865,7 +8865,7 @@
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>1,97%</t>
+          <t>2,08%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -8880,12 +8880,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>6962</t>
+          <t>7143</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>18673</t>
+          <t>18990</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -8895,12 +8895,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>1,0%</t>
+          <t>1,03%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>2,69%</t>
+          <t>2,73%</t>
         </is>
       </c>
     </row>
@@ -8923,12 +8923,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>46844</t>
+          <t>47664</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>71346</t>
+          <t>71415</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -8938,12 +8938,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>13,55%</t>
+          <t>13,79%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>20,64%</t>
+          <t>20,66%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -8958,12 +8958,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>35457</t>
+          <t>35791</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>56786</t>
+          <t>56614</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -8973,12 +8973,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>10,15%</t>
+          <t>10,25%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>16,26%</t>
+          <t>16,21%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -8993,12 +8993,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>87486</t>
+          <t>87960</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>118492</t>
+          <t>118842</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -9008,12 +9008,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>12,59%</t>
+          <t>12,66%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>17,05%</t>
+          <t>17,1%</t>
         </is>
       </c>
     </row>
@@ -9036,12 +9036,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>99111</t>
+          <t>100142</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>128520</t>
+          <t>128006</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -9051,12 +9051,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>28,67%</t>
+          <t>28,97%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>37,18%</t>
+          <t>37,03%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -9071,12 +9071,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>104216</t>
+          <t>105434</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>134083</t>
+          <t>134358</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -9086,12 +9086,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>29,84%</t>
+          <t>30,19%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>38,4%</t>
+          <t>38,48%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -9106,12 +9106,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>213321</t>
+          <t>212435</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>255414</t>
+          <t>255096</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -9121,12 +9121,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>30,7%</t>
+          <t>30,57%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>36,76%</t>
+          <t>36,71%</t>
         </is>
       </c>
     </row>
@@ -9149,12 +9149,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>148101</t>
+          <t>148667</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>179895</t>
+          <t>179183</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -9164,12 +9164,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>42,84%</t>
+          <t>43,01%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>52,04%</t>
+          <t>51,83%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -9184,12 +9184,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>163112</t>
+          <t>163627</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>195184</t>
+          <t>194537</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -9199,12 +9199,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>46,71%</t>
+          <t>46,86%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>55,89%</t>
+          <t>55,71%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -9219,12 +9219,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>321411</t>
+          <t>321812</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>365290</t>
+          <t>365179</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -9234,12 +9234,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>46,25%</t>
+          <t>46,31%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>52,57%</t>
+          <t>52,55%</t>
         </is>
       </c>
     </row>
@@ -9415,7 +9415,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores según frecuencia de sentirse  triste en 2023 (tasa de respuesta: 100,0%)</t>
+          <t>Menores según la frecuencia de sentirse triste en 2023 (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -9615,7 +9615,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>4130</t>
+          <t>3911</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -9630,7 +9630,7 @@
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>33,29%</t>
+          <t>31,53%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -9685,7 +9685,7 @@
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>4200</t>
+          <t>3713</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -9700,7 +9700,7 @@
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>14,4%</t>
+          <t>12,73%</t>
         </is>
       </c>
     </row>
@@ -9763,7 +9763,7 @@
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>3830</t>
+          <t>4902</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -9778,7 +9778,7 @@
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>22,86%</t>
+          <t>29,26%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -9798,7 +9798,7 @@
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>4182</t>
+          <t>4077</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -9813,7 +9813,7 @@
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>14,34%</t>
+          <t>13,98%</t>
         </is>
       </c>
     </row>
@@ -9841,7 +9841,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>3578</t>
+          <t>3795</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -9856,7 +9856,7 @@
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>28,84%</t>
+          <t>30,59%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -9876,7 +9876,7 @@
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>4419</t>
+          <t>4117</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -9891,7 +9891,7 @@
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>26,37%</t>
+          <t>24,57%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -9906,12 +9906,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>665</t>
+          <t>645</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>5835</t>
+          <t>6109</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -9921,12 +9921,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>2,28%</t>
+          <t>2,21%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>20,01%</t>
+          <t>20,95%</t>
         </is>
       </c>
     </row>
@@ -9949,12 +9949,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>1474</t>
+          <t>1593</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>7075</t>
+          <t>6969</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -9964,12 +9964,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>11,88%</t>
+          <t>12,84%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>57,03%</t>
+          <t>56,17%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -9984,12 +9984,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>2748</t>
+          <t>3048</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>10052</t>
+          <t>10050</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -9999,12 +9999,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>16,4%</t>
+          <t>18,19%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>60,0%</t>
+          <t>59,99%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -10019,12 +10019,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>6337</t>
+          <t>5696</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>15161</t>
+          <t>14975</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -10034,12 +10034,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>21,73%</t>
+          <t>19,53%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>51,99%</t>
+          <t>51,35%</t>
         </is>
       </c>
     </row>
@@ -10062,12 +10062,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>3745</t>
+          <t>3475</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>9464</t>
+          <t>9514</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -10077,12 +10077,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>30,18%</t>
+          <t>28,01%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>76,28%</t>
+          <t>76,69%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -10097,12 +10097,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>4547</t>
+          <t>4617</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>12255</t>
+          <t>12262</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -10112,12 +10112,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>27,14%</t>
+          <t>27,55%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>73,15%</t>
+          <t>73,19%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -10132,12 +10132,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>10052</t>
+          <t>9997</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>19293</t>
+          <t>20158</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -10147,12 +10147,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>34,47%</t>
+          <t>34,28%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>66,16%</t>
+          <t>69,13%</t>
         </is>
       </c>
     </row>
@@ -10292,12 +10292,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>645</t>
+          <t>0</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>7773</t>
+          <t>6711</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -10307,12 +10307,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>0,4%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>4,88%</t>
+          <t>4,21%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -10327,12 +10327,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>876</t>
+          <t>776</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>6649</t>
+          <t>6834</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -10342,12 +10342,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>0,43%</t>
+          <t>0,38%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>3,28%</t>
+          <t>3,37%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -10362,12 +10362,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>2012</t>
+          <t>2245</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>10772</t>
+          <t>11168</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -10377,12 +10377,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>0,56%</t>
+          <t>0,62%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>2,98%</t>
+          <t>3,08%</t>
         </is>
       </c>
     </row>
@@ -10410,7 +10410,7 @@
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>6001</t>
+          <t>5102</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -10425,7 +10425,7 @@
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>3,77%</t>
+          <t>3,2%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -10440,12 +10440,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>856</t>
+          <t>917</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>9385</t>
+          <t>9270</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -10455,12 +10455,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>0,42%</t>
+          <t>0,45%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>4,63%</t>
+          <t>4,57%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -10475,12 +10475,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>1692</t>
+          <t>1591</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>11763</t>
+          <t>11649</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -10490,12 +10490,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>0,47%</t>
+          <t>0,44%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>3,25%</t>
+          <t>3,22%</t>
         </is>
       </c>
     </row>
@@ -10518,12 +10518,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>7268</t>
+          <t>7098</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>21995</t>
+          <t>22028</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -10533,12 +10533,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>4,56%</t>
+          <t>4,46%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>13,81%</t>
+          <t>13,83%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -10553,12 +10553,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>21280</t>
+          <t>21523</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>50764</t>
+          <t>51418</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -10568,12 +10568,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>10,5%</t>
+          <t>10,62%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>25,04%</t>
+          <t>25,37%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -10588,12 +10588,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>33427</t>
+          <t>32316</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>66899</t>
+          <t>68480</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -10603,12 +10603,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>9,23%</t>
+          <t>8,93%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>18,48%</t>
+          <t>18,92%</t>
         </is>
       </c>
     </row>
@@ -10631,12 +10631,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>29497</t>
+          <t>27935</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>64360</t>
+          <t>65144</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -10646,12 +10646,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>18,52%</t>
+          <t>17,53%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>40,4%</t>
+          <t>40,89%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -10666,12 +10666,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>41411</t>
+          <t>41215</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>67567</t>
+          <t>67726</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -10681,12 +10681,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>20,43%</t>
+          <t>20,33%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>33,33%</t>
+          <t>33,41%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -10701,12 +10701,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>79528</t>
+          <t>77674</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>122547</t>
+          <t>122730</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -10716,12 +10716,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>21,97%</t>
+          <t>21,46%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>33,85%</t>
+          <t>33,9%</t>
         </is>
       </c>
     </row>
@@ -10744,12 +10744,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>74315</t>
+          <t>74173</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>120452</t>
+          <t>122557</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -10759,12 +10759,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>46,65%</t>
+          <t>46,56%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>75,61%</t>
+          <t>76,93%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -10779,12 +10779,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>92376</t>
+          <t>93186</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>127099</t>
+          <t>126232</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -10794,12 +10794,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>45,57%</t>
+          <t>45,97%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>62,7%</t>
+          <t>62,28%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -10814,12 +10814,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>178248</t>
+          <t>178059</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>237076</t>
+          <t>242684</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -10829,12 +10829,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>49,24%</t>
+          <t>49,19%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>65,49%</t>
+          <t>67,04%</t>
         </is>
       </c>
     </row>
@@ -10979,7 +10979,7 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>4414</t>
+          <t>4104</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -10994,7 +10994,7 @@
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>11,39%</t>
+          <t>10,59%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -11049,7 +11049,7 @@
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>3055</t>
+          <t>3705</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -11064,7 +11064,7 @@
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>3,34%</t>
+          <t>4,05%</t>
         </is>
       </c>
     </row>
@@ -11200,12 +11200,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>1833</t>
+          <t>1874</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>9600</t>
+          <t>10247</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -11215,12 +11215,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>4,73%</t>
+          <t>4,84%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>24,77%</t>
+          <t>26,44%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -11235,12 +11235,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>2046</t>
+          <t>2016</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>9861</t>
+          <t>10399</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -11250,12 +11250,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>3,88%</t>
+          <t>3,83%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>18,71%</t>
+          <t>19,74%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -11270,12 +11270,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>5471</t>
+          <t>5256</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>16723</t>
+          <t>16861</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -11285,12 +11285,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>5,98%</t>
+          <t>5,75%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>18,29%</t>
+          <t>18,44%</t>
         </is>
       </c>
     </row>
@@ -11313,12 +11313,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>5679</t>
+          <t>5154</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>14896</t>
+          <t>14436</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -11328,12 +11328,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>14,65%</t>
+          <t>13,3%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>38,44%</t>
+          <t>37,25%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -11348,12 +11348,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>10162</t>
+          <t>9725</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>22428</t>
+          <t>21465</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -11363,12 +11363,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>19,29%</t>
+          <t>18,46%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>42,56%</t>
+          <t>40,74%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -11383,12 +11383,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>18061</t>
+          <t>18235</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>32978</t>
+          <t>32767</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -11398,12 +11398,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>19,75%</t>
+          <t>19,94%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>36,06%</t>
+          <t>35,83%</t>
         </is>
       </c>
     </row>
@@ -11426,12 +11426,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>18876</t>
+          <t>18918</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>29286</t>
+          <t>28597</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -11441,12 +11441,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>48,71%</t>
+          <t>48,82%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>75,57%</t>
+          <t>73,79%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -11461,12 +11461,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>24796</t>
+          <t>25974</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>38011</t>
+          <t>38692</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -11476,12 +11476,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>47,06%</t>
+          <t>49,29%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>72,14%</t>
+          <t>73,43%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -11496,12 +11496,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>46918</t>
+          <t>48148</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>63750</t>
+          <t>64071</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -11511,12 +11511,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>51,31%</t>
+          <t>52,65%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>69,71%</t>
+          <t>70,06%</t>
         </is>
       </c>
     </row>
@@ -11656,12 +11656,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>1411</t>
+          <t>1457</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>9145</t>
+          <t>8818</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -11671,12 +11671,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>0,67%</t>
+          <t>0,69%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>4,35%</t>
+          <t>4,19%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -11691,12 +11691,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>921</t>
+          <t>948</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>7467</t>
+          <t>7287</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -11706,12 +11706,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>0,34%</t>
+          <t>0,35%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>2,74%</t>
+          <t>2,68%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -11726,12 +11726,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>3030</t>
+          <t>2907</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>11867</t>
+          <t>12423</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -11741,12 +11741,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>0,63%</t>
+          <t>0,6%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>2,46%</t>
+          <t>2,57%</t>
         </is>
       </c>
     </row>
@@ -11774,7 +11774,7 @@
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>4805</t>
+          <t>6781</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -11789,7 +11789,7 @@
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>2,28%</t>
+          <t>3,22%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -11804,12 +11804,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>1673</t>
+          <t>1685</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>10866</t>
+          <t>10748</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -11819,12 +11819,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>0,61%</t>
+          <t>0,62%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>3,99%</t>
+          <t>3,95%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -11839,12 +11839,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>2291</t>
+          <t>2312</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>12202</t>
+          <t>11901</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -11854,12 +11854,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>0,47%</t>
+          <t>0,48%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>2,53%</t>
+          <t>2,47%</t>
         </is>
       </c>
     </row>
@@ -11882,12 +11882,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>11703</t>
+          <t>12354</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>28951</t>
+          <t>28186</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -11897,12 +11897,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>5,56%</t>
+          <t>5,87%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>13,76%</t>
+          <t>13,39%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -11917,12 +11917,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>27413</t>
+          <t>27327</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>57540</t>
+          <t>59010</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -11932,12 +11932,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>10,07%</t>
+          <t>10,04%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>21,14%</t>
+          <t>21,68%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -11952,12 +11952,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>43564</t>
+          <t>42691</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>78920</t>
+          <t>80971</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -11967,12 +11967,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>9,03%</t>
+          <t>8,85%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>16,35%</t>
+          <t>16,78%</t>
         </is>
       </c>
     </row>
@@ -11995,12 +11995,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>39723</t>
+          <t>38866</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>78182</t>
+          <t>77187</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -12010,12 +12010,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>18,87%</t>
+          <t>18,47%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>37,15%</t>
+          <t>36,67%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -12030,12 +12030,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>60667</t>
+          <t>60757</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>91262</t>
+          <t>91568</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -12045,12 +12045,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>22,29%</t>
+          <t>22,33%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>33,53%</t>
+          <t>33,65%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -12065,12 +12065,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>111479</t>
+          <t>112537</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>160231</t>
+          <t>160536</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -12080,12 +12080,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>23,1%</t>
+          <t>23,32%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>33,2%</t>
+          <t>33,26%</t>
         </is>
       </c>
     </row>
@@ -12108,12 +12108,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>103589</t>
+          <t>105315</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>155894</t>
+          <t>157684</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -12123,12 +12123,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>49,22%</t>
+          <t>50,04%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>74,07%</t>
+          <t>74,92%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -12143,12 +12143,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>132144</t>
+          <t>131434</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>170443</t>
+          <t>170829</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -12158,12 +12158,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>48,56%</t>
+          <t>48,3%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>62,63%</t>
+          <t>62,77%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -12178,12 +12178,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>246457</t>
+          <t>245352</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>310916</t>
+          <t>313463</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -12193,12 +12193,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>51,07%</t>
+          <t>50,84%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>64,42%</t>
+          <t>64,95%</t>
         </is>
       </c>
     </row>
